--- a/READING/15_24_07.xlsx
+++ b/READING/15_24_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\READING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A8FA11-E828-4A73-BD6A-3D35F6779A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{265880E5-CCF5-413A-8E76-4FF185D80C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19215" yWindow="1005" windowWidth="19185" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -225,10 +225,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>〜わけにはいかない</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一応</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -506,12 +502,36 @@
     <t>てじゅん</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>わけにはいかない</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,6 +558,29 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -575,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -584,6 +627,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1119,8 +1165,8 @@
       <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>43</v>
+      <c r="E19" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
@@ -1128,10 +1174,10 @@
         <v>0</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
@@ -1139,10 +1185,10 @@
         <v>0</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -1150,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -1161,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -1172,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -1183,13 +1229,13 @@
         <v>0</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
@@ -1197,13 +1243,13 @@
         <v>0</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
@@ -1211,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
@@ -1222,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
@@ -1233,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -1244,10 +1290,10 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
@@ -1255,10 +1301,10 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
@@ -1266,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1277,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
@@ -1288,10 +1334,10 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1299,13 +1345,13 @@
         <v>0</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1313,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1324,13 +1370,13 @@
         <v>0</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1338,10 +1384,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1349,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1360,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1371,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -1382,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1393,10 +1439,10 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1404,10 +1450,10 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1415,13 +1461,13 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1429,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1440,10 +1486,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1451,13 +1497,13 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
